--- a/sixfold/finance/Sixfold-Expenses-and-Profit.xlsx
+++ b/sixfold/finance/Sixfold-Expenses-and-Profit.xlsx
@@ -21,17 +21,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);-"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="$#,##0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="166" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="#,##0.0;(#,##0.0);-"/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +71,15 @@
       <name val="Arial"/>
       <color rgb="00008000"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +104,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4C2"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,12 +181,12 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -184,21 +197,40 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -692,8 +724,8 @@
   <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" style="63" min="1" max="1"/>
+    <col width="110" customWidth="1" style="63" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1000,12 +1032,12 @@
   <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" style="63" min="1" max="1"/>
+    <col width="14" customWidth="1" style="63" min="2" max="2"/>
+    <col width="14" customWidth="1" style="63" min="3" max="3"/>
+    <col width="14" customWidth="1" style="63" min="4" max="4"/>
+    <col width="14" customWidth="1" style="63" min="5" max="5"/>
+    <col width="60" customWidth="1" style="63" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1015,7 +1047,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="30" customHeight="1" s="63">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Money in is when Square took it. Job costs are in the month of the job (Done jobs only). October runs to the 21st. Yellow = still to fill in; until then those costs count as $0, so profit reads high.</t>
@@ -1235,19 +1267,19 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Gas (truck + aerator)</t>
         </is>
       </c>
       <c r="B15" s="15">
-        <f>SUMIFS('Variable per job'!$S$16:$S$34,'Variable per job'!$AB$16:$AB$34,B$5,'Variable per job'!$E$16:$E$34,"Done")</f>
+        <f>SUMIFS('Variable per job'!$S$16:$S$34,'Variable per job'!$AB$16:$AB$34,B$5,'Variable per job'!$E$16:$E$34,"Done")+SUMIFS('Variable per job'!$AC$16:$AC$34,'Variable per job'!$AB$16:$AB$34,B$5,'Variable per job'!$E$16:$E$34,"Done")</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>SUMIFS('Variable per job'!$S$16:$S$34,'Variable per job'!$AB$16:$AB$34,C$5,'Variable per job'!$E$16:$E$34,"Done")</f>
+        <f>SUMIFS('Variable per job'!$S$16:$S$34,'Variable per job'!$AB$16:$AB$34,C$5,'Variable per job'!$E$16:$E$34,"Done")+SUMIFS('Variable per job'!$AC$16:$AC$34,'Variable per job'!$AB$16:$AB$34,C$5,'Variable per job'!$E$16:$E$34,"Done")</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>SUMIFS('Variable per job'!$S$16:$S$34,'Variable per job'!$AB$16:$AB$34,D$5,'Variable per job'!$E$16:$E$34,"Done")</f>
+        <f>SUMIFS('Variable per job'!$S$16:$S$34,'Variable per job'!$AB$16:$AB$34,D$5,'Variable per job'!$E$16:$E$34,"Done")+SUMIFS('Variable per job'!$AC$16:$AC$34,'Variable per job'!$AB$16:$AB$34,D$5,'Variable per job'!$E$16:$E$34,"Done")</f>
         <v/>
       </c>
       <c r="E15" s="16">
@@ -1567,7 +1599,7 @@
           <t>Owed on Done jobs</t>
         </is>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="54">
         <f>SUMIFS('Variable per job'!$I$16:$I$34,'Variable per job'!$E$16:$E$34,"Done")</f>
         <v/>
       </c>
@@ -1583,7 +1615,7 @@
           <t>Booked jobs: price</t>
         </is>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="54">
         <f>SUMIFS('Variable per job'!$G$16:$G$34,'Variable per job'!$E$16:$E$34,"Booked")</f>
         <v/>
       </c>
@@ -1599,7 +1631,7 @@
           <t>Booked jobs: deposits already in</t>
         </is>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="54">
         <f>SUMIFS('Variable per job'!$H$16:$H$34,'Variable per job'!$E$16:$E$34,"Booked")</f>
         <v/>
       </c>
@@ -1610,7 +1642,7 @@
           <t>Booked jobs: still to collect</t>
         </is>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="55">
         <f>B33-B34</f>
         <v/>
       </c>
@@ -1670,15 +1702,15 @@
           <t>Job prices</t>
         </is>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="54">
         <f>SUMIFS('Variable per job'!$G$16:$G$34,'Variable per job'!$E$16:$E$34,"Done",'Variable per job'!$C$16:$C$34,"Sixfold")</f>
         <v/>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="54">
         <f>SUMIFS('Variable per job'!$G$16:$G$34,'Variable per job'!$E$16:$E$34,"Done",'Variable per job'!$C$16:$C$34,"365")</f>
         <v/>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="55">
         <f>B40+C40</f>
         <v/>
       </c>
@@ -1746,15 +1778,15 @@
           <t>Average price per job</t>
         </is>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="55">
         <f>IF(B39=0,0,B40/B39)</f>
         <v/>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="55">
         <f>IF(C39=0,0,C40/C39)</f>
         <v/>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="55">
         <f>IF(D39=0,0,D40/D39)</f>
         <v/>
       </c>
@@ -1784,10 +1816,10 @@
           <t>Week starting (a Monday)</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="56" t="n">
         <v>46307</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="57">
         <f>B49+6</f>
         <v/>
       </c>
@@ -1903,17 +1935,17 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" style="63" min="1" max="1"/>
+    <col width="22" customWidth="1" style="63" min="2" max="2"/>
+    <col width="11" customWidth="1" style="63" min="3" max="3"/>
+    <col width="14" customWidth="1" style="63" min="4" max="4"/>
+    <col width="11" customWidth="1" style="63" min="5" max="5"/>
+    <col width="11" customWidth="1" style="63" min="6" max="6"/>
+    <col width="14" customWidth="1" style="63" min="7" max="7"/>
+    <col width="13" customWidth="1" style="63" min="8" max="8"/>
+    <col width="14" customWidth="1" style="63" min="9" max="9"/>
+    <col width="13" customWidth="1" style="63" min="10" max="10"/>
+    <col width="70" customWidth="1" style="63" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1930,7 +1962,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="32" customHeight="1" s="63">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Item</t>
@@ -3055,7 +3087,7 @@
           <t>Business cards (printed)</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n"/>
+      <c r="B36" s="56" t="n"/>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="14">
         <f>IF(B36="","",TEXT(B36,"yyyy-mm"))</f>
@@ -3073,7 +3105,7 @@
           <t>Yard signs (FedEx print)</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n"/>
+      <c r="B37" s="56" t="n"/>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="14">
         <f>IF(B37="","",TEXT(B37,"yyyy-mm"))</f>
@@ -3087,7 +3119,7 @@
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr"/>
-      <c r="B38" s="29" t="n"/>
+      <c r="B38" s="56" t="n"/>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="14">
         <f>IF(B38="","",TEXT(B38,"yyyy-mm"))</f>
@@ -3097,7 +3129,7 @@
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr"/>
-      <c r="B39" s="29" t="n"/>
+      <c r="B39" s="56" t="n"/>
       <c r="C39" s="19" t="n"/>
       <c r="D39" s="14">
         <f>IF(B39="","",TEXT(B39,"yyyy-mm"))</f>
@@ -3107,7 +3139,7 @@
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr"/>
-      <c r="B40" s="29" t="n"/>
+      <c r="B40" s="56" t="n"/>
       <c r="C40" s="19" t="n"/>
       <c r="D40" s="14">
         <f>IF(B40="","",TEXT(B40,"yyyy-mm"))</f>
@@ -3117,7 +3149,7 @@
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr"/>
-      <c r="B41" s="29" t="n"/>
+      <c r="B41" s="56" t="n"/>
       <c r="C41" s="19" t="n"/>
       <c r="D41" s="14">
         <f>IF(B41="","",TEXT(B41,"yyyy-mm"))</f>
@@ -3147,14 +3179,14 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" style="63" min="1" max="1"/>
+    <col width="34" customWidth="1" style="63" min="2" max="2"/>
+    <col width="20" customWidth="1" style="63" min="3" max="3"/>
+    <col width="12" customWidth="1" style="63" min="4" max="4"/>
+    <col width="14" customWidth="1" style="63" min="5" max="5"/>
+    <col width="14" customWidth="1" style="63" min="6" max="6"/>
+    <col width="16" customWidth="1" style="63" min="7" max="7"/>
+    <col width="60" customWidth="1" style="63" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3164,14 +3196,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="42" customHeight="1" s="63">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>The crew on each job costs 20% of the job price, set on the Variable per job tab. Use this tab only for pay NOT tied to a job: "Hourly" = rate x hours a month; "Salary (monthly)" = the month's pay; "Per job" or "Not paid" = nothing extra here.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="32" customHeight="1" s="63">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Name</t>
@@ -3416,19 +3448,19 @@
   <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" style="63" min="1" max="1"/>
+    <col width="9" customWidth="1" style="63" min="2" max="2"/>
+    <col width="18" customWidth="1" style="63" min="3" max="3"/>
+    <col width="10" customWidth="1" style="63" min="4" max="4"/>
+    <col width="9" customWidth="1" style="63" min="5" max="5"/>
+    <col width="12" customWidth="1" style="63" min="6" max="6"/>
+    <col width="12" customWidth="1" style="63" min="7" max="7"/>
+    <col width="12" customWidth="1" style="63" min="8" max="8"/>
+    <col width="12" customWidth="1" style="63" min="9" max="9"/>
+    <col width="14" customWidth="1" style="63" min="10" max="10"/>
+    <col width="18" customWidth="1" style="63" min="11" max="11"/>
+    <col width="14" customWidth="1" style="63" min="12" max="12"/>
+    <col width="52" customWidth="1" style="63" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3445,7 +3477,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="32" customHeight="1" s="63">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Date</t>
@@ -3513,7 +3545,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="n">
+      <c r="A5" s="58" t="n">
         <v>46265</v>
       </c>
       <c r="B5" s="14">
@@ -3564,7 +3596,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="n">
+      <c r="A6" s="58" t="n">
         <v>46267</v>
       </c>
       <c r="B6" s="14">
@@ -3604,7 +3636,7 @@
         <v/>
       </c>
       <c r="K6" s="35" t="n"/>
-      <c r="L6" s="29" t="n"/>
+      <c r="L6" s="56" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>A check entered in Square. Which job? (question 7)</t>
@@ -3612,7 +3644,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="n">
+      <c r="A7" s="58" t="n">
         <v>46281</v>
       </c>
       <c r="B7" s="14">
@@ -3656,7 +3688,7 @@
           <t>Kara R.</t>
         </is>
       </c>
-      <c r="L7" s="39" t="n">
+      <c r="L7" s="58" t="n">
         <v>46282</v>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -3666,7 +3698,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="n">
+      <c r="A8" s="58" t="n">
         <v>46283</v>
       </c>
       <c r="B8" s="14">
@@ -3710,7 +3742,7 @@
           <t>Kara R.</t>
         </is>
       </c>
-      <c r="L8" s="39" t="n">
+      <c r="L8" s="58" t="n">
         <v>46282</v>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -3720,7 +3752,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="n">
+      <c r="A9" s="58" t="n">
         <v>46301</v>
       </c>
       <c r="B9" s="14">
@@ -3764,7 +3796,7 @@
           <t>Kara R.</t>
         </is>
       </c>
-      <c r="L9" s="39" t="n">
+      <c r="L9" s="58" t="n">
         <v>46307</v>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -3774,7 +3806,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="n">
+      <c r="A10" s="58" t="n">
         <v>46302</v>
       </c>
       <c r="B10" s="14">
@@ -3818,7 +3850,7 @@
           <t>Brian S.</t>
         </is>
       </c>
-      <c r="L10" s="39" t="n">
+      <c r="L10" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -3828,7 +3860,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="n">
+      <c r="A11" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B11" s="14">
@@ -3872,7 +3904,7 @@
           <t>Kara R.</t>
         </is>
       </c>
-      <c r="L11" s="39" t="n">
+      <c r="L11" s="58" t="n">
         <v>46307</v>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -3882,7 +3914,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="n">
+      <c r="A12" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B12" s="14">
@@ -3926,7 +3958,7 @@
           <t>Kirk C.</t>
         </is>
       </c>
-      <c r="L12" s="39" t="n">
+      <c r="L12" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -3936,7 +3968,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="n">
+      <c r="A13" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B13" s="14">
@@ -3980,7 +4012,7 @@
           <t>Russ K.</t>
         </is>
       </c>
-      <c r="L13" s="39" t="n">
+      <c r="L13" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -3990,7 +4022,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="n">
+      <c r="A14" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B14" s="14">
@@ -4034,7 +4066,7 @@
           <t>Eric V.</t>
         </is>
       </c>
-      <c r="L14" s="39" t="n">
+      <c r="L14" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -4044,7 +4076,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="n">
+      <c r="A15" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B15" s="14">
@@ -4088,7 +4120,7 @@
           <t>Carlos P.</t>
         </is>
       </c>
-      <c r="L15" s="39" t="n">
+      <c r="L15" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -4098,7 +4130,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="n">
+      <c r="A16" s="58" t="n">
         <v>46313</v>
       </c>
       <c r="B16" s="14">
@@ -4142,7 +4174,7 @@
           <t>Sreenivas K.</t>
         </is>
       </c>
-      <c r="L16" s="39" t="n">
+      <c r="L16" s="58" t="n">
         <v>46318</v>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -4152,7 +4184,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="n">
+      <c r="A17" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B17" s="14">
@@ -4196,7 +4228,7 @@
           <t>Kirk C.</t>
         </is>
       </c>
-      <c r="L17" s="39" t="n">
+      <c r="L17" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -4206,7 +4238,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="n">
+      <c r="A18" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B18" s="14">
@@ -4250,7 +4282,7 @@
           <t>Randy C.</t>
         </is>
       </c>
-      <c r="L18" s="39" t="n">
+      <c r="L18" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -4260,7 +4292,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="n">
+      <c r="A19" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B19" s="14">
@@ -4304,7 +4336,7 @@
           <t>Joseph B.</t>
         </is>
       </c>
-      <c r="L19" s="39" t="n">
+      <c r="L19" s="58" t="n">
         <v>46325</v>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -4314,7 +4346,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="n">
+      <c r="A20" s="58" t="n">
         <v>46316</v>
       </c>
       <c r="B20" s="14">
@@ -4358,7 +4390,7 @@
           <t>Jeremy</t>
         </is>
       </c>
-      <c r="L20" s="39" t="n">
+      <c r="L20" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="M20" s="11" t="inlineStr">
@@ -4368,7 +4400,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="n"/>
+      <c r="A21" s="59" t="n"/>
       <c r="B21" s="14">
         <f>IF(A21="","",TEXT(A21,"yyyy-mm"))</f>
         <v/>
@@ -4384,10 +4416,10 @@
         <f>IF(F21="","",N(I21)-N(H21))</f>
         <v/>
       </c>
-      <c r="L21" s="40" t="n"/>
+      <c r="L21" s="59" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="n"/>
+      <c r="A22" s="59" t="n"/>
       <c r="B22" s="14">
         <f>IF(A22="","",TEXT(A22,"yyyy-mm"))</f>
         <v/>
@@ -4403,10 +4435,10 @@
         <f>IF(F22="","",N(I22)-N(H22))</f>
         <v/>
       </c>
-      <c r="L22" s="40" t="n"/>
+      <c r="L22" s="59" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="n"/>
+      <c r="A23" s="59" t="n"/>
       <c r="B23" s="14">
         <f>IF(A23="","",TEXT(A23,"yyyy-mm"))</f>
         <v/>
@@ -4422,10 +4454,10 @@
         <f>IF(F23="","",N(I23)-N(H23))</f>
         <v/>
       </c>
-      <c r="L23" s="40" t="n"/>
+      <c r="L23" s="59" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="n"/>
+      <c r="A24" s="59" t="n"/>
       <c r="B24" s="14">
         <f>IF(A24="","",TEXT(A24,"yyyy-mm"))</f>
         <v/>
@@ -4441,10 +4473,10 @@
         <f>IF(F24="","",N(I24)-N(H24))</f>
         <v/>
       </c>
-      <c r="L24" s="40" t="n"/>
+      <c r="L24" s="59" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="n"/>
+      <c r="A25" s="59" t="n"/>
       <c r="B25" s="14">
         <f>IF(A25="","",TEXT(A25,"yyyy-mm"))</f>
         <v/>
@@ -4460,10 +4492,10 @@
         <f>IF(F25="","",N(I25)-N(H25))</f>
         <v/>
       </c>
-      <c r="L25" s="40" t="n"/>
+      <c r="L25" s="59" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="n"/>
+      <c r="A26" s="59" t="n"/>
       <c r="B26" s="14">
         <f>IF(A26="","",TEXT(A26,"yyyy-mm"))</f>
         <v/>
@@ -4479,7 +4511,7 @@
         <f>IF(F26="","",N(I26)-N(H26))</f>
         <v/>
       </c>
-      <c r="L26" s="40" t="n"/>
+      <c r="L26" s="59" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -4537,37 +4569,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" style="63" min="1" max="1"/>
+    <col width="13" customWidth="1" style="63" min="2" max="2"/>
+    <col width="9" customWidth="1" style="63" min="3" max="3"/>
+    <col width="12" customWidth="1" style="63" min="4" max="4"/>
+    <col width="9" customWidth="1" style="63" min="5" max="5"/>
+    <col width="15" customWidth="1" style="63" min="6" max="6"/>
+    <col width="10" customWidth="1" style="63" min="7" max="7"/>
+    <col width="11" customWidth="1" style="63" min="8" max="8"/>
+    <col width="10" customWidth="1" style="63" min="9" max="9"/>
+    <col width="9" customWidth="1" style="63" min="10" max="10"/>
+    <col width="15" customWidth="1" style="63" min="11" max="11"/>
+    <col width="9" customWidth="1" style="63" min="12" max="12"/>
+    <col width="9" customWidth="1" style="63" min="13" max="13"/>
+    <col width="9" customWidth="1" style="63" min="14" max="14"/>
+    <col width="9" customWidth="1" style="63" min="15" max="15"/>
+    <col width="9" customWidth="1" style="63" min="16" max="16"/>
+    <col width="9" customWidth="1" style="63" min="17" max="17"/>
+    <col width="11" customWidth="1" style="63" min="18" max="18"/>
+    <col width="9" customWidth="1" style="63" min="19" max="19"/>
+    <col width="10" customWidth="1" style="63" min="20" max="20"/>
+    <col width="10" customWidth="1" style="63" min="21" max="21"/>
+    <col width="10" customWidth="1" style="63" min="22" max="22"/>
+    <col width="11" customWidth="1" style="63" min="23" max="23"/>
+    <col width="10" customWidth="1" style="63" min="24" max="24"/>
+    <col width="10" customWidth="1" style="63" min="25" max="25"/>
+    <col width="11" customWidth="1" style="63" min="26" max="26"/>
+    <col width="8" customWidth="1" style="63" min="27" max="27"/>
+    <col width="9" customWidth="1" style="63" min="28" max="28"/>
+    <col width="11" customWidth="1" style="63" min="29" max="29"/>
+    <col width="40" customWidth="1" style="63" min="30" max="30"/>
+    <col width="11" customWidth="1" style="63" min="31" max="31"/>
+    <col width="60" customWidth="1" style="63" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4581,6 +4617,13 @@
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Seed, fertilizer, gas, Square fees and crew pay for each job, and what each job made. Inputs first; the jobs table is below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="60" t="inlineStr">
+        <is>
+          <t>Aerator gas inputs are at the right of the table (columns AD to AF).</t>
         </is>
       </c>
     </row>
@@ -4617,6 +4660,11 @@
       <c r="Z4" s="17" t="n"/>
       <c r="AA4" s="17" t="n"/>
       <c r="AB4" s="17" t="n"/>
+      <c r="AD4" s="61" t="inlineStr">
+        <is>
+          <t>Aerator gas inputs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -4632,6 +4680,19 @@
           <t>SiteOne Englewood invoice 2026-07-24: 6 x 50 lb LESCO Tuf-Turf Seed Mixture, $773.34 with tax.</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Aerator: fuel tank (gal)</t>
+        </is>
+      </c>
+      <c r="AE5" s="62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Bobcat AE26-HON spec page (new.bobcat.com, read 2026-10-21): 0.5 gal. Honda lists the GX120 tank as 2.0 L.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -4647,6 +4708,19 @@
           <t>Same invoice.</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Aerator: fuel burn (gal per hour)</t>
+        </is>
+      </c>
+      <c r="AE6" s="64" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Honda GX120: 1.0 L/h at rated power (3,600 rpm), as republished by Honda dealers; not found on Honda’s own site. Full throttle: the most it burns.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -4654,12 +4728,25 @@
           <t>Seed: lb per 1,000 sq ft when not recorded</t>
         </is>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="65" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
           <t>The app's middle seeding rate (Bryce's 2 to 4 lb range; CSU says 3 to 4 after aeration).</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Aerator: coverage (sq ft per hour)</t>
+        </is>
+      </c>
+      <c r="AE7" s="66" t="n">
+        <v>40400</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Bobcat AE26 maximum productivity at 3.5 mph, 26.5 in wide. No turns, trees or overlap: real jobs are slower.</t>
         </is>
       </c>
     </row>
@@ -4677,6 +4764,19 @@
           <t>Matthew, 21 Oct 2026: $40 for a 50 lb bag.</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Aerator: real pace (share of Bobcat’s top rate)</t>
+        </is>
+      </c>
+      <c r="AE8" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Yours to set. 100% = Bobcat’s figure (the least gas). Lower it once fill-ups show what a tank really covers.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -4692,6 +4792,20 @@
           <t>Label.</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Aerator: sq ft per tank</t>
+        </is>
+      </c>
+      <c r="AE9" s="66">
+        <f>AE5/AE6*AE7*AE8</f>
+        <v/>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Worked out: tank / burn x coverage x pace.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -4714,7 +4828,7 @@
           <t>Gas: price per gallon ($)</t>
         </is>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="68" t="n">
         <v>4.244</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -4744,7 +4858,7 @@
           <t>Road miles per straight-line mile</t>
         </is>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D13" s="69" t="n">
         <v>1.3</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -4768,7 +4882,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="45" customHeight="1" s="63">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Date</t>
@@ -4909,9 +5023,14 @@
           <t>Month</t>
         </is>
       </c>
+      <c r="AC15" s="31" t="inlineStr">
+        <is>
+          <t>Aerator gas ($)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="n">
+      <c r="A16" s="58" t="n">
         <v>46282</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -4935,13 +5054,13 @@
         </is>
       </c>
       <c r="F16" s="35" t="inlineStr"/>
-      <c r="G16" s="46" t="n">
+      <c r="G16" s="70" t="n">
         <v>1500</v>
       </c>
-      <c r="H16" s="46" t="n">
+      <c r="H16" s="70" t="n">
         <v>1500</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="55">
         <f>G16-H16</f>
         <v/>
       </c>
@@ -4973,7 +5092,7 @@
         <f>P16*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R16" s="49" t="n"/>
+      <c r="R16" s="71" t="n"/>
       <c r="S16" s="16">
         <f>IF(T16&lt;&gt;"",N(T16),N(R16)*$D$13*2/$D$12*$D$11)</f>
         <v/>
@@ -4990,7 +5109,7 @@
         <v/>
       </c>
       <c r="Y16" s="16">
-        <f>N16+Q16+S16+U16+N(V16)+X16</f>
+        <f>N16+Q16+S16+U16+N(V16)+X16+N(AC16)</f>
         <v/>
       </c>
       <c r="Z16" s="16">
@@ -5005,9 +5124,13 @@
         <f>TEXT(A16,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC16" s="41">
+        <f>N(J16)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="n">
+      <c r="A17" s="58" t="n">
         <v>46307</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -5031,13 +5154,13 @@
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr"/>
-      <c r="G17" s="46" t="n">
+      <c r="G17" s="70" t="n">
         <v>1100</v>
       </c>
-      <c r="H17" s="46" t="n">
+      <c r="H17" s="70" t="n">
         <v>1100</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="55">
         <f>G17-H17</f>
         <v/>
       </c>
@@ -5065,7 +5188,7 @@
         <f>P17*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R17" s="49" t="n"/>
+      <c r="R17" s="71" t="n"/>
       <c r="S17" s="16">
         <f>IF(T17&lt;&gt;"",N(T17),N(R17)*$D$13*2/$D$12*$D$11)</f>
         <v/>
@@ -5082,7 +5205,7 @@
         <v/>
       </c>
       <c r="Y17" s="16">
-        <f>N17+Q17+S17+U17+N(V17)+X17</f>
+        <f>N17+Q17+S17+U17+N(V17)+X17+N(AC17)</f>
         <v/>
       </c>
       <c r="Z17" s="16">
@@ -5097,9 +5220,13 @@
         <f>TEXT(A17,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC17" s="41">
+        <f>N(J17)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="n">
+      <c r="A18" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -5127,13 +5254,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G18" s="46" t="n">
+      <c r="G18" s="70" t="n">
         <v>400</v>
       </c>
-      <c r="H18" s="46" t="n">
+      <c r="H18" s="70" t="n">
         <v>200</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="55">
         <f>G18-H18</f>
         <v/>
       </c>
@@ -5161,7 +5288,7 @@
         <f>P18*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R18" s="43" t="n">
+      <c r="R18" s="65" t="n">
         <v>17.23</v>
       </c>
       <c r="S18" s="16">
@@ -5180,7 +5307,7 @@
         <v/>
       </c>
       <c r="Y18" s="16">
-        <f>N18+Q18+S18+U18+N(V18)+X18</f>
+        <f>N18+Q18+S18+U18+N(V18)+X18+N(AC18)</f>
         <v/>
       </c>
       <c r="Z18" s="16">
@@ -5195,9 +5322,13 @@
         <f>TEXT(A18,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC18" s="41">
+        <f>N(J18)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="n">
+      <c r="A19" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5225,13 +5356,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G19" s="46" t="n">
+      <c r="G19" s="70" t="n">
         <v>200</v>
       </c>
-      <c r="H19" s="46" t="n">
+      <c r="H19" s="70" t="n">
         <v>200</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="55">
         <f>G19-H19</f>
         <v/>
       </c>
@@ -5261,7 +5392,7 @@
         <f>P19*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R19" s="43" t="n">
+      <c r="R19" s="65" t="n">
         <v>8.91</v>
       </c>
       <c r="S19" s="16">
@@ -5280,7 +5411,7 @@
         <v/>
       </c>
       <c r="Y19" s="16">
-        <f>N19+Q19+S19+U19+N(V19)+X19</f>
+        <f>N19+Q19+S19+U19+N(V19)+X19+N(AC19)</f>
         <v/>
       </c>
       <c r="Z19" s="16">
@@ -5295,9 +5426,13 @@
         <f>TEXT(A19,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC19" s="41">
+        <f>N(J19)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="n">
+      <c r="A20" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -5325,13 +5460,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G20" s="46" t="n">
+      <c r="G20" s="70" t="n">
         <v>200</v>
       </c>
-      <c r="H20" s="46" t="n">
+      <c r="H20" s="70" t="n">
         <v>200</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="55">
         <f>G20-H20</f>
         <v/>
       </c>
@@ -5361,7 +5496,7 @@
         <f>P20*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R20" s="43" t="n">
+      <c r="R20" s="65" t="n">
         <v>8.92</v>
       </c>
       <c r="S20" s="16">
@@ -5380,7 +5515,7 @@
         <v/>
       </c>
       <c r="Y20" s="16">
-        <f>N20+Q20+S20+U20+N(V20)+X20</f>
+        <f>N20+Q20+S20+U20+N(V20)+X20+N(AC20)</f>
         <v/>
       </c>
       <c r="Z20" s="16">
@@ -5395,9 +5530,13 @@
         <f>TEXT(A20,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC20" s="41">
+        <f>N(J20)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="n">
+      <c r="A21" s="58" t="n">
         <v>46311</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -5425,13 +5564,13 @@
           <t>Brandon Long</t>
         </is>
       </c>
-      <c r="G21" s="46" t="n">
+      <c r="G21" s="70" t="n">
         <v>175</v>
       </c>
-      <c r="H21" s="46" t="n">
+      <c r="H21" s="70" t="n">
         <v>175</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="55">
         <f>G21-H21</f>
         <v/>
       </c>
@@ -5465,7 +5604,7 @@
         <f>P21*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R21" s="49" t="n"/>
+      <c r="R21" s="71" t="n"/>
       <c r="S21" s="16">
         <f>IF(T21&lt;&gt;"",N(T21),N(R21)*$D$13*2/$D$12*$D$11)</f>
         <v/>
@@ -5482,7 +5621,7 @@
         <v/>
       </c>
       <c r="Y21" s="16">
-        <f>N21+Q21+S21+U21+N(V21)+X21</f>
+        <f>N21+Q21+S21+U21+N(V21)+X21+N(AC21)</f>
         <v/>
       </c>
       <c r="Z21" s="16">
@@ -5497,9 +5636,13 @@
         <f>TEXT(A21,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC21" s="41">
+        <f>N(J21)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="n">
+      <c r="A22" s="58" t="n">
         <v>46314</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -5527,13 +5670,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G22" s="46" t="n">
+      <c r="G22" s="70" t="n">
         <v>299</v>
       </c>
-      <c r="H22" s="46" t="n">
+      <c r="H22" s="70" t="n">
         <v>299</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="55">
         <f>G22-H22</f>
         <v/>
       </c>
@@ -5563,7 +5706,7 @@
         <f>P22*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R22" s="43" t="n">
+      <c r="R22" s="65" t="n">
         <v>16.04</v>
       </c>
       <c r="S22" s="16">
@@ -5582,7 +5725,7 @@
         <v/>
       </c>
       <c r="Y22" s="16">
-        <f>N22+Q22+S22+U22+N(V22)+X22</f>
+        <f>N22+Q22+S22+U22+N(V22)+X22+N(AC22)</f>
         <v/>
       </c>
       <c r="Z22" s="16">
@@ -5597,9 +5740,13 @@
         <f>TEXT(A22,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC22" s="41">
+        <f>N(J22)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="n">
+      <c r="A23" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -5627,13 +5774,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G23" s="46" t="n">
+      <c r="G23" s="70" t="n">
         <v>350</v>
       </c>
-      <c r="H23" s="46" t="n">
+      <c r="H23" s="70" t="n">
         <v>350</v>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="55">
         <f>G23-H23</f>
         <v/>
       </c>
@@ -5667,7 +5814,7 @@
         <f>P23*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R23" s="43" t="n">
+      <c r="R23" s="65" t="n">
         <v>12.78</v>
       </c>
       <c r="S23" s="16">
@@ -5686,7 +5833,7 @@
         <v/>
       </c>
       <c r="Y23" s="16">
-        <f>N23+Q23+S23+U23+N(V23)+X23</f>
+        <f>N23+Q23+S23+U23+N(V23)+X23+N(AC23)</f>
         <v/>
       </c>
       <c r="Z23" s="16">
@@ -5701,9 +5848,13 @@
         <f>TEXT(A23,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC23" s="41">
+        <f>N(J23)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="n">
+      <c r="A24" s="58" t="n">
         <v>46315</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -5731,13 +5882,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G24" s="46" t="n">
+      <c r="G24" s="70" t="n">
         <v>468</v>
       </c>
-      <c r="H24" s="46" t="n">
+      <c r="H24" s="70" t="n">
         <v>468</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="55">
         <f>G24-H24</f>
         <v/>
       </c>
@@ -5771,7 +5922,7 @@
         <f>P24*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R24" s="43" t="n">
+      <c r="R24" s="65" t="n">
         <v>13.07</v>
       </c>
       <c r="S24" s="16">
@@ -5790,7 +5941,7 @@
         <v/>
       </c>
       <c r="Y24" s="16">
-        <f>N24+Q24+S24+U24+N(V24)+X24</f>
+        <f>N24+Q24+S24+U24+N(V24)+X24+N(AC24)</f>
         <v/>
       </c>
       <c r="Z24" s="16">
@@ -5805,9 +5956,13 @@
         <f>TEXT(A24,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC24" s="41">
+        <f>N(J24)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="n">
+      <c r="A25" s="58" t="n">
         <v>46318</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -5835,13 +5990,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G25" s="46" t="n">
+      <c r="G25" s="70" t="n">
         <v>339</v>
       </c>
-      <c r="H25" s="46" t="n">
+      <c r="H25" s="70" t="n">
         <v>50</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="55">
         <f>G25-H25</f>
         <v/>
       </c>
@@ -5871,7 +6026,7 @@
         <f>P25*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R25" s="43" t="n">
+      <c r="R25" s="65" t="n">
         <v>9.24</v>
       </c>
       <c r="S25" s="16">
@@ -5890,7 +6045,7 @@
         <v/>
       </c>
       <c r="Y25" s="16">
-        <f>N25+Q25+S25+U25+N(V25)+X25</f>
+        <f>N25+Q25+S25+U25+N(V25)+X25+N(AC25)</f>
         <v/>
       </c>
       <c r="Z25" s="16">
@@ -5905,9 +6060,13 @@
         <f>TEXT(A25,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC25" s="41">
+        <f>N(J25)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="n">
+      <c r="A26" s="58" t="n">
         <v>46325</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -5935,13 +6094,13 @@
           <t>Brad McPherson</t>
         </is>
       </c>
-      <c r="G26" s="46" t="n">
+      <c r="G26" s="70" t="n">
         <v>814</v>
       </c>
-      <c r="H26" s="46" t="n">
+      <c r="H26" s="70" t="n">
         <v>200</v>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="55">
         <f>G26-H26</f>
         <v/>
       </c>
@@ -5969,7 +6128,7 @@
         <f>P26*($D$8/$D$9)</f>
         <v/>
       </c>
-      <c r="R26" s="49" t="n"/>
+      <c r="R26" s="71" t="n"/>
       <c r="S26" s="16">
         <f>IF(T26&lt;&gt;"",N(T26),N(R26)*$D$13*2/$D$12*$D$11)</f>
         <v/>
@@ -5986,7 +6145,7 @@
         <v/>
       </c>
       <c r="Y26" s="16">
-        <f>N26+Q26+S26+U26+N(V26)+X26</f>
+        <f>N26+Q26+S26+U26+N(V26)+X26+N(AC26)</f>
         <v/>
       </c>
       <c r="Z26" s="16">
@@ -6001,12 +6160,16 @@
         <f>TEXT(A26,"yyyy-mm")</f>
         <v/>
       </c>
+      <c r="AC26" s="41">
+        <f>N(J26)/($AE$7*$AE$8)*$AE$6*$D$11</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="n"/>
+      <c r="A27" s="59" t="n"/>
       <c r="G27" s="41" t="n"/>
       <c r="H27" s="41" t="n"/>
-      <c r="I27" s="26">
+      <c r="I27" s="55">
         <f>IF(G27="","",G27-N(H27))</f>
         <v/>
       </c>
@@ -6042,7 +6205,7 @@
         <v/>
       </c>
       <c r="Y27" s="16">
-        <f>IF(G27="","",N(N27)+N(Q27)+N(S27)+N(U27)+N(V27)+N(X27))</f>
+        <f>IF(G27="","",N(N27)+N(Q27)+N(S27)+N(U27)+N(V27)+N(X27)+N(AC27))</f>
         <v/>
       </c>
       <c r="Z27" s="16">
@@ -6057,12 +6220,16 @@
         <f>IF(A27="","",TEXT(A27,"yyyy-mm"))</f>
         <v/>
       </c>
+      <c r="AC27" s="41">
+        <f>IF(G27="","",N(J27)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="n"/>
+      <c r="A28" s="59" t="n"/>
       <c r="G28" s="41" t="n"/>
       <c r="H28" s="41" t="n"/>
-      <c r="I28" s="26">
+      <c r="I28" s="55">
         <f>IF(G28="","",G28-N(H28))</f>
         <v/>
       </c>
@@ -6098,7 +6265,7 @@
         <v/>
       </c>
       <c r="Y28" s="16">
-        <f>IF(G28="","",N(N28)+N(Q28)+N(S28)+N(U28)+N(V28)+N(X28))</f>
+        <f>IF(G28="","",N(N28)+N(Q28)+N(S28)+N(U28)+N(V28)+N(X28)+N(AC28))</f>
         <v/>
       </c>
       <c r="Z28" s="16">
@@ -6113,12 +6280,16 @@
         <f>IF(A28="","",TEXT(A28,"yyyy-mm"))</f>
         <v/>
       </c>
+      <c r="AC28" s="41">
+        <f>IF(G28="","",N(J28)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="n"/>
+      <c r="A29" s="59" t="n"/>
       <c r="G29" s="41" t="n"/>
       <c r="H29" s="41" t="n"/>
-      <c r="I29" s="26">
+      <c r="I29" s="55">
         <f>IF(G29="","",G29-N(H29))</f>
         <v/>
       </c>
@@ -6154,7 +6325,7 @@
         <v/>
       </c>
       <c r="Y29" s="16">
-        <f>IF(G29="","",N(N29)+N(Q29)+N(S29)+N(U29)+N(V29)+N(X29))</f>
+        <f>IF(G29="","",N(N29)+N(Q29)+N(S29)+N(U29)+N(V29)+N(X29)+N(AC29))</f>
         <v/>
       </c>
       <c r="Z29" s="16">
@@ -6169,12 +6340,16 @@
         <f>IF(A29="","",TEXT(A29,"yyyy-mm"))</f>
         <v/>
       </c>
+      <c r="AC29" s="41">
+        <f>IF(G29="","",N(J29)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="n"/>
+      <c r="A30" s="59" t="n"/>
       <c r="G30" s="41" t="n"/>
       <c r="H30" s="41" t="n"/>
-      <c r="I30" s="26">
+      <c r="I30" s="55">
         <f>IF(G30="","",G30-N(H30))</f>
         <v/>
       </c>
@@ -6210,7 +6385,7 @@
         <v/>
       </c>
       <c r="Y30" s="16">
-        <f>IF(G30="","",N(N30)+N(Q30)+N(S30)+N(U30)+N(V30)+N(X30))</f>
+        <f>IF(G30="","",N(N30)+N(Q30)+N(S30)+N(U30)+N(V30)+N(X30)+N(AC30))</f>
         <v/>
       </c>
       <c r="Z30" s="16">
@@ -6225,12 +6400,16 @@
         <f>IF(A30="","",TEXT(A30,"yyyy-mm"))</f>
         <v/>
       </c>
+      <c r="AC30" s="41">
+        <f>IF(G30="","",N(J30)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="n"/>
+      <c r="A31" s="59" t="n"/>
       <c r="G31" s="41" t="n"/>
       <c r="H31" s="41" t="n"/>
-      <c r="I31" s="26">
+      <c r="I31" s="55">
         <f>IF(G31="","",G31-N(H31))</f>
         <v/>
       </c>
@@ -6266,7 +6445,7 @@
         <v/>
       </c>
       <c r="Y31" s="16">
-        <f>IF(G31="","",N(N31)+N(Q31)+N(S31)+N(U31)+N(V31)+N(X31))</f>
+        <f>IF(G31="","",N(N31)+N(Q31)+N(S31)+N(U31)+N(V31)+N(X31)+N(AC31))</f>
         <v/>
       </c>
       <c r="Z31" s="16">
@@ -6281,12 +6460,16 @@
         <f>IF(A31="","",TEXT(A31,"yyyy-mm"))</f>
         <v/>
       </c>
+      <c r="AC31" s="41">
+        <f>IF(G31="","",N(J31)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="n"/>
+      <c r="A32" s="59" t="n"/>
       <c r="G32" s="41" t="n"/>
       <c r="H32" s="41" t="n"/>
-      <c r="I32" s="26">
+      <c r="I32" s="55">
         <f>IF(G32="","",G32-N(H32))</f>
         <v/>
       </c>
@@ -6322,7 +6505,7 @@
         <v/>
       </c>
       <c r="Y32" s="16">
-        <f>IF(G32="","",N(N32)+N(Q32)+N(S32)+N(U32)+N(V32)+N(X32))</f>
+        <f>IF(G32="","",N(N32)+N(Q32)+N(S32)+N(U32)+N(V32)+N(X32)+N(AC32))</f>
         <v/>
       </c>
       <c r="Z32" s="16">
@@ -6337,12 +6520,16 @@
         <f>IF(A32="","",TEXT(A32,"yyyy-mm"))</f>
         <v/>
       </c>
+      <c r="AC32" s="41">
+        <f>IF(G32="","",N(J32)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="n"/>
+      <c r="A33" s="59" t="n"/>
       <c r="G33" s="41" t="n"/>
       <c r="H33" s="41" t="n"/>
-      <c r="I33" s="26">
+      <c r="I33" s="55">
         <f>IF(G33="","",G33-N(H33))</f>
         <v/>
       </c>
@@ -6378,7 +6565,7 @@
         <v/>
       </c>
       <c r="Y33" s="16">
-        <f>IF(G33="","",N(N33)+N(Q33)+N(S33)+N(U33)+N(V33)+N(X33))</f>
+        <f>IF(G33="","",N(N33)+N(Q33)+N(S33)+N(U33)+N(V33)+N(X33)+N(AC33))</f>
         <v/>
       </c>
       <c r="Z33" s="16">
@@ -6393,12 +6580,16 @@
         <f>IF(A33="","",TEXT(A33,"yyyy-mm"))</f>
         <v/>
       </c>
+      <c r="AC33" s="41">
+        <f>IF(G33="","",N(J33)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="n"/>
+      <c r="A34" s="59" t="n"/>
       <c r="G34" s="41" t="n"/>
       <c r="H34" s="41" t="n"/>
-      <c r="I34" s="26">
+      <c r="I34" s="55">
         <f>IF(G34="","",G34-N(H34))</f>
         <v/>
       </c>
@@ -6434,7 +6625,7 @@
         <v/>
       </c>
       <c r="Y34" s="16">
-        <f>IF(G34="","",N(N34)+N(Q34)+N(S34)+N(U34)+N(V34)+N(X34))</f>
+        <f>IF(G34="","",N(N34)+N(Q34)+N(S34)+N(U34)+N(V34)+N(X34)+N(AC34))</f>
         <v/>
       </c>
       <c r="Z34" s="16">
@@ -6447,6 +6638,10 @@
       </c>
       <c r="AB34" s="14">
         <f>IF(A34="","",TEXT(A34,"yyyy-mm"))</f>
+        <v/>
+      </c>
+      <c r="AC34" s="41">
+        <f>IF(G34="","",N(J34)/($AE$7*$AE$8)*$AE$6*$D$11)</f>
         <v/>
       </c>
     </row>
@@ -6461,15 +6656,15 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="23" t="n"/>
       <c r="F35" s="23" t="n"/>
-      <c r="G35" s="51">
+      <c r="G35" s="72">
         <f>SUM(G16:G34)</f>
         <v/>
       </c>
-      <c r="H35" s="51">
+      <c r="H35" s="72">
         <f>SUM(H16:H34)</f>
         <v/>
       </c>
-      <c r="I35" s="51">
+      <c r="I35" s="72">
         <f>SUM(I16:I34)</f>
         <v/>
       </c>
@@ -6529,7 +6724,7 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Square fees come from the Payments tab by customer. Crew pay comes from the Employees tab unless you type an override. Collected and price are from the app. Seed and fertilizer lb: Jen's quote where recorded, otherwise the lawn size x the rates above.</t>
+          <t>Square fees come from the Payments tab by customer. Crew pay comes from the Employees tab unless you type an override. Collected and price are from the app. Seed and fertilizer lb: Jen's quote where recorded, otherwise the lawn size x the rates above. Aerator gas: lawn sq ft over the Bobcat’s coverage, times its fuel per hour and the gas price (inputs at AD5:AE9); a job with no lawn size has none.</t>
         </is>
       </c>
     </row>
